--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="72">
   <si>
     <t>Division</t>
   </si>
@@ -50,130 +50,184 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>DM2</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREBIERES BC - 1 (4) </t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>JEAN DEGROS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>DFU15-8</t>
+  </si>
+  <si>
+    <t>25654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET CLUB PEVELE (2) </t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>DFU18-2</t>
+  </si>
+  <si>
+    <t>6915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (6) </t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>PRM</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET CLUB PEVELE (4) </t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>DMU11-8</t>
+  </si>
+  <si>
+    <t>28402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORCHESIEN B C - 2 (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>LEO LAGRANGE</t>
+  </si>
+  <si>
+    <t>DMU15-2</t>
+  </si>
+  <si>
+    <t>8961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONNAING JA (3) </t>
+  </si>
+  <si>
+    <t>Daniel COLMONT</t>
+  </si>
+  <si>
+    <t>DMU18-2</t>
+  </si>
+  <si>
+    <t>4617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST AMAND P H (3) </t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>MAURICE HUGOT</t>
+  </si>
+  <si>
+    <t>M9XEW737</t>
+  </si>
+  <si>
+    <t>DFU13-2</t>
+  </si>
+  <si>
+    <t>11255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (4) </t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>DMU13-8</t>
+  </si>
+  <si>
+    <t>27059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET (5) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
+  </si>
+  <si>
+    <t>Jules LADOUMEGUE</t>
+  </si>
+  <si>
     <t>AMIU13F</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT (26) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
-  </si>
-  <si>
-    <t>06/09/2026</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>CZJ8U7ED</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Non</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
-    <t xml:space="preserve">TOURCOING US F (16) </t>
+    <t xml:space="preserve">TOURCOING US F (33) </t>
   </si>
   <si>
     <t>13/09/2026</t>
   </si>
   <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>AMILOISIRS</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET CLUB HULLUCH (2) </t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>THF8X6GZ</t>
-  </si>
-  <si>
-    <t>AMISM</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (58) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAINT SAULVE BC (13) </t>
-  </si>
-  <si>
-    <t>12/09/2026</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THIANT BC (25) </t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>JEAN DEGROS</t>
-  </si>
-  <si>
-    <t>ZUKWCAJX</t>
-  </si>
-  <si>
-    <t>AMIU18M</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (19) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNION DECHY SIN BASKET (20) </t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>L3XF6NMK</t>
-  </si>
-  <si>
-    <t>AMIU13M</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (23) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AULNOY VALENCIENNES S (24) </t>
-  </si>
-  <si>
-    <t>97EDTAHL</t>
+    <t>TDPM3DC4</t>
+  </si>
+  <si>
+    <t>DFU11-8</t>
+  </si>
+  <si>
+    <t>29251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AULNOY VALENCIENNES S (2) </t>
+  </si>
+  <si>
+    <t>14:00</t>
   </si>
 </sst>
 </file>
@@ -219,16 +273,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="9.91796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="8.1796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.29296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="44.19921875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="31.32421875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="33.890625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="45.765625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.27734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.65234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.8515625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="16.3359375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="10.9296875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="6.83203125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="7.4765625" customWidth="true" bestFit="true"/>
@@ -293,9 +347,11 @@
       <c r="F2" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="G2" s="0"/>
+      <c r="G2" t="s" s="0">
+        <v>18</v>
+      </c>
       <c r="H2" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>19</v>
@@ -304,7 +360,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s" s="0">
         <v>20</v>
@@ -312,35 +368,37 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>22</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="G3" s="0"/>
+      <c r="G3" t="s" s="0">
+        <v>18</v>
+      </c>
       <c r="H3" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L3" t="s" s="0">
         <v>20</v>
@@ -348,35 +406,37 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="C4" t="s" s="0">
         <v>28</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>15</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>29</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="G4" s="0"/>
+        <v>31</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>18</v>
+      </c>
       <c r="H4" t="s" s="0">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L4" t="s" s="0">
         <v>20</v>
@@ -396,23 +456,25 @@
         <v>35</v>
       </c>
       <c r="E5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="F5" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="G5" s="0"/>
+      <c r="G5" t="s" s="0">
+        <v>18</v>
+      </c>
       <c r="H5" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>20</v>
@@ -420,37 +482,37 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>20</v>
@@ -467,26 +529,28 @@
         <v>45</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="G7" s="0"/>
+        <v>36</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>46</v>
+      </c>
       <c r="H7" t="s" s="0">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s" s="0">
         <v>20</v>
@@ -494,37 +558,189 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="D8" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="C8" t="s" s="0">
+      <c r="G8" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="D8" t="s" s="0">
+      <c r="H8" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="E8" t="s" s="0">
+      <c r="I8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="F8" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="G8" s="0"/>
-      <c r="H8" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="I8" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="J8" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="K8" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="L8" t="s" s="0">
+      <c r="F9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="G11" s="0"/>
+      <c r="H11" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="L12" t="s" s="0">
         <v>20</v>
       </c>
     </row>

--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
   <si>
     <t>Division</t>
   </si>
@@ -50,184 +50,250 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>DXU9-8</t>
+  </si>
+  <si>
+    <t>29985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLINES LEZ RACHES BC - 1 (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
+  </si>
+  <si>
+    <t>27/09/2026</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>Marcel CERDAN</t>
+  </si>
+  <si>
+    <t>MJ8FUQFH</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
     <t>DM2</t>
   </si>
   <si>
-    <t>570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BREBIERES BC - 1 (4) </t>
-  </si>
-  <si>
-    <t>19/09/2026</t>
-  </si>
-  <si>
-    <t>20:30</t>
+    <t>601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC LESQUIN - 2 (6) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (5) </t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>FABRICE COURCIER</t>
+  </si>
+  <si>
+    <t>PRM</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIMBEAUCOURT CSL - 1 (6) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (4) </t>
+  </si>
+  <si>
+    <t>Raymond DAPVRIL</t>
+  </si>
+  <si>
+    <t>DMU18-2</t>
+  </si>
+  <si>
+    <t>4617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST AMAND P H (2) </t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>MAURICE HUGOT</t>
+  </si>
+  <si>
+    <t>M9XEW737</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>DFU18-2</t>
+  </si>
+  <si>
+    <t>6938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORIGNIES DOUAI AAE (5) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>Théo BOUTON</t>
+  </si>
+  <si>
+    <t>DMU15-2</t>
+  </si>
+  <si>
+    <t>8972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AULNOYE AS (1) </t>
+  </si>
+  <si>
+    <t>26/09/2026</t>
+  </si>
+  <si>
+    <t>17:00</t>
   </si>
   <si>
     <t>JEAN DEGROS</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Non</t>
+    <t>DFU13-2</t>
+  </si>
+  <si>
+    <t>11262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPLEUVE L P - 3 (5) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
+  </si>
+  <si>
+    <t>SALLE DES SPORTS (SALLE A)</t>
+  </si>
+  <si>
+    <t>4642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIMBEAUCOURT CSL (6) </t>
+  </si>
+  <si>
+    <t>DFU11-8</t>
+  </si>
+  <si>
+    <t>29269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 1 (1) </t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>S. ALLENDE</t>
   </si>
   <si>
     <t>DFU15-8</t>
   </si>
   <si>
-    <t>25654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET CLUB PEVELE (2) </t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>DFU18-2</t>
+    <t>25672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (2) </t>
+  </si>
+  <si>
+    <t>Jules LADOUMEGUE</t>
   </si>
   <si>
     <t>6915</t>
   </si>
   <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (6) </t>
-  </si>
-  <si>
-    <t>20/09/2026</t>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (3) </t>
   </si>
   <si>
     <t>10:30</t>
   </si>
   <si>
-    <t>PRM</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET CLUB PEVELE (4) </t>
-  </si>
-  <si>
-    <t>18:30</t>
+    <t>D3YY9JVN</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>AMILOISIRS</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (5) </t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>DMU13-8</t>
+  </si>
+  <si>
+    <t>27089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMBRES BASKET CLUB - 1 (2) </t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>DFU9-8</t>
+  </si>
+  <si>
+    <t>30811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET (5) </t>
+  </si>
+  <si>
+    <t>11:00</t>
   </si>
   <si>
     <t>DMU11-8</t>
   </si>
   <si>
-    <t>28402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORCHESIEN B C - 2 (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>LEO LAGRANGE</t>
-  </si>
-  <si>
-    <t>DMU15-2</t>
-  </si>
-  <si>
-    <t>8961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONNAING JA (3) </t>
-  </si>
-  <si>
-    <t>Daniel COLMONT</t>
-  </si>
-  <si>
-    <t>DMU18-2</t>
-  </si>
-  <si>
-    <t>4617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST AMAND P H (3) </t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>MAURICE HUGOT</t>
-  </si>
-  <si>
-    <t>M9XEW737</t>
-  </si>
-  <si>
-    <t>DFU13-2</t>
-  </si>
-  <si>
-    <t>11255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (4) </t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>DMU13-8</t>
-  </si>
-  <si>
-    <t>27059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNION DECHY SIN BASKET (5) </t>
+    <t>28431</t>
   </si>
   <si>
     <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
   </si>
   <si>
-    <t>Jules LADOUMEGUE</t>
-  </si>
-  <si>
-    <t>AMIU13F</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOURCOING US F (33) </t>
-  </si>
-  <si>
-    <t>13/09/2026</t>
-  </si>
-  <si>
-    <t>TDPM3DC4</t>
-  </si>
-  <si>
-    <t>DFU11-8</t>
-  </si>
-  <si>
-    <t>29251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AULNOY VALENCIENNES S (2) </t>
-  </si>
-  <si>
-    <t>14:00</t>
+    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT - 1 (4) </t>
   </si>
 </sst>
 </file>
@@ -273,16 +339,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="9.91796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.29296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="33.890625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="45.765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="45.765625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="43.93359375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.27734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.65234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.3359375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="24.26171875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="10.9296875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="6.83203125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="7.4765625" customWidth="true" bestFit="true"/>
@@ -354,394 +420,546 @@
         <v>19</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>31</v>
-      </c>
       <c r="G4" t="s" s="0">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="B9" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>56</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>57</v>
-      </c>
       <c r="G9" t="s" s="0">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="G11" s="0"/>
+        <v>53</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>71</v>
+      </c>
       <c r="H11" t="s" s="0">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L11" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L12" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="G13" s="0"/>
+      <c r="H13" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I13" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="L14" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="L15" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I16" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="L16" t="s" s="0">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="105">
   <si>
     <t>Division</t>
   </si>
@@ -50,250 +50,283 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>PRM</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET CLUB PEVELE (3) </t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>JEAN DEGROS</t>
+  </si>
+  <si>
+    <t>QN8J7AVW</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>DFU18-2</t>
+  </si>
+  <si>
+    <t>6915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (3) </t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>D3YY9JVN</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>DFU15-8</t>
+  </si>
+  <si>
+    <t>25654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET CLUB PEVELE (4) </t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>LQ2HN8DD</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>DXU9-8</t>
   </si>
   <si>
-    <t>29985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLINES LEZ RACHES BC - 1 (3) </t>
+    <t>29959</t>
   </si>
   <si>
     <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
   </si>
   <si>
-    <t>27/09/2026</t>
+    <t xml:space="preserve">ST AMAND P H (2) </t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>QC49F93L</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>DFU11-8</t>
+  </si>
+  <si>
+    <t>29251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AULNOY VALENCIENNES S (4) </t>
   </si>
   <si>
     <t>14:00</t>
   </si>
   <si>
-    <t>Marcel CERDAN</t>
-  </si>
-  <si>
-    <t>MJ8FUQFH</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Non</t>
+    <t>47WQM4RU</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>DFU9-8</t>
+  </si>
+  <si>
+    <t>30804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONNAING JA - 1 (3) </t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>BEATRICE HEISS</t>
+  </si>
+  <si>
+    <t>PH4BW29F</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>DMU18-2</t>
+  </si>
+  <si>
+    <t>4617</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>MAURICE HUGOT</t>
+  </si>
+  <si>
+    <t>M9XEW737</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>DMU11-8</t>
+  </si>
+  <si>
+    <t>28402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORCHESIEN B C - 2 (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
+  </si>
+  <si>
+    <t>LEO LAGRANGE</t>
+  </si>
+  <si>
+    <t>WXEC6PRG</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>DFU13-2</t>
+  </si>
+  <si>
+    <t>11255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (6) </t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>QTZXCP4K</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>DMU15-2</t>
+  </si>
+  <si>
+    <t>8961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONNAING JA (2) </t>
+  </si>
+  <si>
+    <t>Daniel COLMONT</t>
+  </si>
+  <si>
+    <t>P3TWKBF6</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>DMU13-8</t>
+  </si>
+  <si>
+    <t>27059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET (4) </t>
+  </si>
+  <si>
+    <t>C.S. J MERCIER</t>
+  </si>
+  <si>
+    <t>DH7ZJNQK</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>51</t>
   </si>
   <si>
     <t>DM2</t>
   </si>
   <si>
-    <t>601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC LESQUIN - 2 (6) </t>
+    <t>570</t>
   </si>
   <si>
     <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (5) </t>
   </si>
   <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>FABRICE COURCIER</t>
-  </si>
-  <si>
-    <t>PRM</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAIMBEAUCOURT CSL - 1 (6) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (4) </t>
-  </si>
-  <si>
-    <t>Raymond DAPVRIL</t>
-  </si>
-  <si>
-    <t>DMU18-2</t>
-  </si>
-  <si>
-    <t>4617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST AMAND P H (2) </t>
-  </si>
-  <si>
-    <t>20/09/2026</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>MAURICE HUGOT</t>
-  </si>
-  <si>
-    <t>M9XEW737</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>DFU18-2</t>
-  </si>
-  <si>
-    <t>6938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DORIGNIES DOUAI AAE (5) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>Théo BOUTON</t>
-  </si>
-  <si>
-    <t>DMU15-2</t>
-  </si>
-  <si>
-    <t>8972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AULNOYE AS (1) </t>
-  </si>
-  <si>
-    <t>26/09/2026</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>JEAN DEGROS</t>
-  </si>
-  <si>
-    <t>DFU13-2</t>
-  </si>
-  <si>
-    <t>11262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEMPLEUVE L P - 3 (5) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
-  </si>
-  <si>
-    <t>SALLE DES SPORTS (SALLE A)</t>
-  </si>
-  <si>
-    <t>4642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAIMBEAUCOURT CSL (6) </t>
-  </si>
-  <si>
-    <t>DFU11-8</t>
-  </si>
-  <si>
-    <t>29269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 1 (1) </t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>S. ALLENDE</t>
-  </si>
-  <si>
-    <t>DFU15-8</t>
-  </si>
-  <si>
-    <t>25672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNION DECHY SIN BASKET (1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (2) </t>
-  </si>
-  <si>
-    <t>Jules LADOUMEGUE</t>
-  </si>
-  <si>
-    <t>6915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (3) </t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>D3YY9JVN</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>AMILOISIRS</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (5) </t>
-  </si>
-  <si>
-    <t>23/09/2026</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>DMU13-8</t>
-  </si>
-  <si>
-    <t>27089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMBRES BASKET CLUB - 1 (2) </t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>DFU9-8</t>
-  </si>
-  <si>
-    <t>30811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNION DECHY SIN BASKET (5) </t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>DMU11-8</t>
-  </si>
-  <si>
-    <t>28431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT - 1 (4) </t>
+    <t xml:space="preserve">BREBIERES BC - 1 (2) </t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>2VD66VPN</t>
+  </si>
+  <si>
+    <t>72</t>
   </si>
 </sst>
 </file>
@@ -339,16 +372,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="9.91796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="8.1796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.29296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="45.765625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="43.93359375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="33.890625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="45.765625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.27734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.65234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="24.26171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="14.37109375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="10.9296875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="6.83203125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="7.4765625" customWidth="true" bestFit="true"/>
@@ -426,7 +459,7 @@
         <v>21</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s" s="0">
         <v>21</v>
@@ -434,37 +467,37 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s" s="0">
         <v>21</v>
@@ -472,37 +505,37 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="L4" t="s" s="0">
         <v>21</v>
@@ -510,37 +543,37 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>21</v>
@@ -548,37 +581,37 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="J6" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>21</v>
@@ -586,37 +619,37 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="L7" t="s" s="0">
         <v>21</v>
@@ -624,37 +657,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="J8" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="L8" t="s" s="0">
         <v>21</v>
@@ -662,37 +695,37 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="J9" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="L9" t="s" s="0">
         <v>21</v>
@@ -700,37 +733,37 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J10" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="L10" t="s" s="0">
         <v>21</v>
@@ -738,37 +771,37 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J11" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="L11" t="s" s="0">
         <v>21</v>
@@ -776,37 +809,37 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="J12" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="L12" t="s" s="0">
         <v>21</v>
@@ -814,151 +847,39 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="G13" s="0"/>
+        <v>102</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>18</v>
+      </c>
       <c r="H13" t="s" s="0">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="L13" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="E14" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="F14" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="G14" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="H14" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="I14" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="J14" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="L14" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="F15" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="G15" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="H15" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="I15" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="J15" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K15" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="L15" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="G16" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="H16" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="I16" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="J16" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="L16" t="s" s="0">
         <v>21</v>
       </c>
     </row>

--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -50,6 +50,66 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>DFU15-8</t>
+  </si>
+  <si>
+    <t>25654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET CLUB PEVELE (4) </t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>JEAN DEGROS</t>
+  </si>
+  <si>
+    <t>LQ2HN8DD</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>DFU18-2</t>
+  </si>
+  <si>
+    <t>6915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (3) </t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>D3YY9JVN</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>PRM</t>
   </si>
   <si>
@@ -62,76 +122,175 @@
     <t xml:space="preserve">BASKET CLUB PEVELE (3) </t>
   </si>
   <si>
-    <t>19/09/2026</t>
-  </si>
-  <si>
     <t>18:30</t>
   </si>
   <si>
-    <t>JEAN DEGROS</t>
-  </si>
-  <si>
     <t>QN8J7AVW</t>
   </si>
   <si>
     <t>55</t>
   </si>
   <si>
-    <t>Non</t>
-  </si>
-  <si>
     <t>56</t>
   </si>
   <si>
-    <t>DFU18-2</t>
-  </si>
-  <si>
-    <t>6915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (3) </t>
-  </si>
-  <si>
-    <t>20/09/2026</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>D3YY9JVN</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>DFU15-8</t>
-  </si>
-  <si>
-    <t>25654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET CLUB PEVELE (4) </t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>LQ2HN8DD</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>DM2</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (5) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREBIERES BC - 1 (2) </t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>2VD66VPN</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>DMU15-2</t>
+  </si>
+  <si>
+    <t>8961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONNAING JA (2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
+  </si>
+  <si>
+    <t>Daniel COLMONT</t>
+  </si>
+  <si>
+    <t>P3TWKBF6</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>DMU18-2</t>
+  </si>
+  <si>
+    <t>4617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST AMAND P H (2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>MAURICE HUGOT</t>
+  </si>
+  <si>
+    <t>M9XEW737</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>DFU13-2</t>
+  </si>
+  <si>
+    <t>11255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (6) </t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>QTZXCP4K</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>DMU11-8</t>
+  </si>
+  <si>
+    <t>28402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORCHESIEN B C - 2 (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>LEO LAGRANGE</t>
+  </si>
+  <si>
+    <t>WXEC6PRG</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>DFU9-8</t>
+  </si>
+  <si>
+    <t>30804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONNAING JA - 1 (3) </t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>BEATRICE HEISS</t>
+  </si>
+  <si>
+    <t>PH4BW29F</t>
+  </si>
+  <si>
+    <t>DMU13-8</t>
+  </si>
+  <si>
+    <t>27059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET (4) </t>
+  </si>
+  <si>
+    <t>C.S. J MERCIER</t>
+  </si>
+  <si>
+    <t>DH7ZJNQK</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>51</t>
   </si>
   <si>
     <t>DXU9-8</t>
@@ -140,15 +299,6 @@
     <t>29959</t>
   </si>
   <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST AMAND P H (2) </t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
     <t>QC49F93L</t>
   </si>
   <si>
@@ -164,9 +314,6 @@
     <t>29251</t>
   </si>
   <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
-  </si>
-  <si>
     <t xml:space="preserve">AULNOY VALENCIENNES S (4) </t>
   </si>
   <si>
@@ -180,153 +327,6 @@
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>DFU9-8</t>
-  </si>
-  <si>
-    <t>30804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONNAING JA - 1 (3) </t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>BEATRICE HEISS</t>
-  </si>
-  <si>
-    <t>PH4BW29F</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>DMU18-2</t>
-  </si>
-  <si>
-    <t>4617</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>MAURICE HUGOT</t>
-  </si>
-  <si>
-    <t>M9XEW737</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>DMU11-8</t>
-  </si>
-  <si>
-    <t>28402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORCHESIEN B C - 2 (1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
-  </si>
-  <si>
-    <t>LEO LAGRANGE</t>
-  </si>
-  <si>
-    <t>WXEC6PRG</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>DFU13-2</t>
-  </si>
-  <si>
-    <t>11255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (6) </t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>QTZXCP4K</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>DMU15-2</t>
-  </si>
-  <si>
-    <t>8961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONNAING JA (2) </t>
-  </si>
-  <si>
-    <t>Daniel COLMONT</t>
-  </si>
-  <si>
-    <t>P3TWKBF6</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>DMU13-8</t>
-  </si>
-  <si>
-    <t>27059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNION DECHY SIN BASKET (4) </t>
-  </si>
-  <si>
-    <t>C.S. J MERCIER</t>
-  </si>
-  <si>
-    <t>DH7ZJNQK</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>DM2</t>
-  </si>
-  <si>
-    <t>570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (5) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BREBIERES BC - 1 (2) </t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>2VD66VPN</t>
-  </si>
-  <si>
-    <t>72</t>
   </si>
 </sst>
 </file>
@@ -596,10 +596,10 @@
         <v>16</v>
       </c>
       <c r="F6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s" s="0">
         <v>52</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>18</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>53</v>
@@ -611,7 +611,7 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>21</v>
@@ -619,19 +619,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="C7" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="D7" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="D7" t="s" s="0">
-        <v>25</v>
-      </c>
       <c r="E7" t="s" s="0">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>59</v>
@@ -643,13 +643,13 @@
         <v>61</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s" s="0">
         <v>21</v>
@@ -657,37 +657,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="J8" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s" s="0">
         <v>21</v>
@@ -695,37 +695,37 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J9" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s" s="0">
         <v>21</v>
@@ -733,37 +733,37 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="0">
         <v>79</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="I10" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="J10" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s" s="0">
-        <v>83</v>
       </c>
       <c r="L10" t="s" s="0">
         <v>21</v>
@@ -771,37 +771,37 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L11" t="s" s="0">
         <v>21</v>
@@ -809,25 +809,25 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>95</v>
@@ -853,25 +853,25 @@
         <v>99</v>
       </c>
       <c r="C13" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="D13" t="s" s="0">
+      <c r="E13" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s" s="0">
         <v>101</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>102</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>18</v>
       </c>
       <c r="H13" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="I13" t="s" s="0">
         <v>103</v>
-      </c>
-      <c r="I13" t="s" s="0">
-        <v>90</v>
       </c>
       <c r="J13" t="s" s="0">
         <v>21</v>

--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -50,6 +50,207 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>DMU13-8</t>
+  </si>
+  <si>
+    <t>27059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>C.S. J MERCIER</t>
+  </si>
+  <si>
+    <t>DH7ZJNQK</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>DMU11-8</t>
+  </si>
+  <si>
+    <t>28402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORCHESIEN B C - 2 (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>LEO LAGRANGE</t>
+  </si>
+  <si>
+    <t>WXEC6PRG</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>DFU13-2</t>
+  </si>
+  <si>
+    <t>11255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (6) </t>
+  </si>
+  <si>
+    <t>JEAN DEGROS</t>
+  </si>
+  <si>
+    <t>QTZXCP4K</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>DMU18-2</t>
+  </si>
+  <si>
+    <t>4617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST AMAND P H (2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>MAURICE HUGOT</t>
+  </si>
+  <si>
+    <t>M9XEW737</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>DMU15-2</t>
+  </si>
+  <si>
+    <t>8961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONNAING JA (2) </t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>Daniel COLMONT</t>
+  </si>
+  <si>
+    <t>P3TWKBF6</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>DFU9-8</t>
+  </si>
+  <si>
+    <t>30804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONNAING JA - 1 (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>BEATRICE HEISS</t>
+  </si>
+  <si>
+    <t>PH4BW29F</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>PRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET CLUB PEVELE (3) </t>
+  </si>
+  <si>
+    <t>QN8J7AVW</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>DFU18-2</t>
+  </si>
+  <si>
+    <t>6915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (3) </t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>D3YY9JVN</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>DFU15-8</t>
   </si>
   <si>
@@ -62,76 +263,28 @@
     <t xml:space="preserve">BASKET CLUB PEVELE (4) </t>
   </si>
   <si>
-    <t>19/09/2026</t>
-  </si>
-  <si>
     <t>17:00</t>
   </si>
   <si>
-    <t>JEAN DEGROS</t>
-  </si>
-  <si>
     <t>LQ2HN8DD</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>Non</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
-    <t>DFU18-2</t>
-  </si>
-  <si>
-    <t>6915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (3) </t>
-  </si>
-  <si>
-    <t>20/09/2026</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>D3YY9JVN</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>PRM</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (4) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET CLUB PEVELE (3) </t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>QN8J7AVW</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>56</t>
+    <t>DXU9-8</t>
+  </si>
+  <si>
+    <t>29959</t>
+  </si>
+  <si>
+    <t>QC49F93L</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
   <si>
     <t>DM2</t>
@@ -152,160 +305,7 @@
     <t>2VD66VPN</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
     <t>72</t>
-  </si>
-  <si>
-    <t>DMU15-2</t>
-  </si>
-  <si>
-    <t>8961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONNAING JA (2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
-  </si>
-  <si>
-    <t>Daniel COLMONT</t>
-  </si>
-  <si>
-    <t>P3TWKBF6</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>DMU18-2</t>
-  </si>
-  <si>
-    <t>4617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST AMAND P H (2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>MAURICE HUGOT</t>
-  </si>
-  <si>
-    <t>M9XEW737</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>DFU13-2</t>
-  </si>
-  <si>
-    <t>11255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (6) </t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>QTZXCP4K</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>DMU11-8</t>
-  </si>
-  <si>
-    <t>28402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORCHESIEN B C - 2 (1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>LEO LAGRANGE</t>
-  </si>
-  <si>
-    <t>WXEC6PRG</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>DFU9-8</t>
-  </si>
-  <si>
-    <t>30804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONNAING JA - 1 (3) </t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>BEATRICE HEISS</t>
-  </si>
-  <si>
-    <t>PH4BW29F</t>
-  </si>
-  <si>
-    <t>DMU13-8</t>
-  </si>
-  <si>
-    <t>27059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNION DECHY SIN BASKET (4) </t>
-  </si>
-  <si>
-    <t>C.S. J MERCIER</t>
-  </si>
-  <si>
-    <t>DH7ZJNQK</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>DXU9-8</t>
-  </si>
-  <si>
-    <t>29959</t>
-  </si>
-  <si>
-    <t>QC49F93L</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>26</t>
   </si>
   <si>
     <t>DFU11-8</t>
@@ -479,13 +479,13 @@
         <v>26</v>
       </c>
       <c r="E3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="F3" t="s" s="0">
+      <c r="G3" t="s" s="0">
         <v>28</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>18</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>29</v>
@@ -520,10 +520,10 @@
         <v>16</v>
       </c>
       <c r="F4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>36</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>18</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>37</v>
@@ -555,25 +555,25 @@
         <v>43</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>21</v>
@@ -581,37 +581,37 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J6" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>21</v>
@@ -619,37 +619,37 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="L7" t="s" s="0">
         <v>21</v>
@@ -657,37 +657,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>65</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>69</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L8" t="s" s="0">
         <v>21</v>
@@ -695,37 +695,37 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>75</v>
       </c>
       <c r="G9" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="H9" t="s" s="0">
+      <c r="I9" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="I9" t="s" s="0">
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s" s="0">
         <v>78</v>
-      </c>
-      <c r="J9" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s" s="0">
-        <v>79</v>
       </c>
       <c r="L9" t="s" s="0">
         <v>21</v>
@@ -733,16 +733,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="C10" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="C10" t="s" s="0">
+      <c r="D10" t="s" s="0">
         <v>82</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>25</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>16</v>
@@ -751,19 +751,19 @@
         <v>83</v>
       </c>
       <c r="G10" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="H10" t="s" s="0">
+      <c r="I10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="0">
         <v>85</v>
-      </c>
-      <c r="I10" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="J10" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s" s="0">
-        <v>79</v>
       </c>
       <c r="L10" t="s" s="0">
         <v>21</v>
@@ -777,31 +777,31 @@
         <v>87</v>
       </c>
       <c r="C11" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="H11" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="D11" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="G11" t="s" s="0">
+      <c r="I11" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="H11" t="s" s="0">
+      <c r="J11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s" s="0">
         <v>90</v>
-      </c>
-      <c r="I11" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="J11" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K11" t="s" s="0">
-        <v>92</v>
       </c>
       <c r="L11" t="s" s="0">
         <v>21</v>
@@ -809,31 +809,31 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="D12" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="C12" t="s" s="0">
-        <v>58</v>
-      </c>
-      <c r="D12" t="s" s="0">
+      <c r="E12" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="I12" t="s" s="0">
         <v>57</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>75</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="H12" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="I12" t="s" s="0">
-        <v>96</v>
       </c>
       <c r="J12" t="s" s="0">
         <v>21</v>
@@ -853,7 +853,7 @@
         <v>99</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>100</v>
@@ -865,7 +865,7 @@
         <v>101</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>102</v>

--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -50,6 +50,87 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>DXU9-8</t>
+  </si>
+  <si>
+    <t>29959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST AMAND P H (1) </t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>JEAN DEGROS</t>
+  </si>
+  <si>
+    <t>QC49F93L</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>DM2</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (5) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREBIERES BC - 1 (1) </t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>2VD66VPN</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>DMU15-2</t>
+  </si>
+  <si>
+    <t>8961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONNAING JA (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>Daniel COLMONT</t>
+  </si>
+  <si>
+    <t>P3TWKBF6</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
     <t>DMU13-8</t>
   </si>
   <si>
@@ -62,9 +143,6 @@
     <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
   </si>
   <si>
-    <t>19/09/2026</t>
-  </si>
-  <si>
     <t>15:30</t>
   </si>
   <si>
@@ -77,12 +155,33 @@
     <t>32</t>
   </si>
   <si>
-    <t>Non</t>
-  </si>
-  <si>
     <t>51</t>
   </si>
   <si>
+    <t>DFU9-8</t>
+  </si>
+  <si>
+    <t>30804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONNAING JA - 1 (4) </t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>BEATRICE HEISS</t>
+  </si>
+  <si>
+    <t>PH4BW29F</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>DMU11-8</t>
   </si>
   <si>
@@ -92,130 +191,88 @@
     <t xml:space="preserve">ORCHESIEN B C - 2 (1) </t>
   </si>
   <si>
+    <t>LEO LAGRANGE</t>
+  </si>
+  <si>
+    <t>WXEC6PRG</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>DMU18-2</t>
+  </si>
+  <si>
+    <t>4617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST AMAND P H (2) </t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>MAURICE HUGOT</t>
+  </si>
+  <si>
+    <t>M9XEW737</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>DFU13-2</t>
+  </si>
+  <si>
+    <t>11255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (6) </t>
+  </si>
+  <si>
+    <t>QTZXCP4K</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>DFU18-2</t>
+  </si>
+  <si>
+    <t>6915</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
   </si>
   <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>LEO LAGRANGE</t>
-  </si>
-  <si>
-    <t>WXEC6PRG</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>DFU13-2</t>
-  </si>
-  <si>
-    <t>11255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (6) </t>
-  </si>
-  <si>
-    <t>JEAN DEGROS</t>
-  </si>
-  <si>
-    <t>QTZXCP4K</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>DMU18-2</t>
-  </si>
-  <si>
-    <t>4617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST AMAND P H (2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
-  </si>
-  <si>
-    <t>20/09/2026</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>MAURICE HUGOT</t>
-  </si>
-  <si>
-    <t>M9XEW737</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>DMU15-2</t>
-  </si>
-  <si>
-    <t>8961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONNAING JA (2) </t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>Daniel COLMONT</t>
-  </si>
-  <si>
-    <t>P3TWKBF6</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>DFU9-8</t>
-  </si>
-  <si>
-    <t>30804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONNAING JA - 1 (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>BEATRICE HEISS</t>
-  </si>
-  <si>
-    <t>PH4BW29F</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (1) </t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>D3YY9JVN</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>42</t>
   </si>
   <si>
     <t>PRM</t>
   </si>
   <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (4) </t>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (5) </t>
   </si>
   <si>
     <t xml:space="preserve">BASKET CLUB PEVELE (3) </t>
@@ -230,27 +287,6 @@
     <t>56</t>
   </si>
   <si>
-    <t>DFU18-2</t>
-  </si>
-  <si>
-    <t>6915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (3) </t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>D3YY9JVN</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
     <t>DFU15-8</t>
   </si>
   <si>
@@ -260,7 +296,7 @@
     <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (2) </t>
   </si>
   <si>
-    <t xml:space="preserve">BASKET CLUB PEVELE (4) </t>
+    <t xml:space="preserve">BASKET CLUB PEVELE (5) </t>
   </si>
   <si>
     <t>17:00</t>
@@ -272,49 +308,13 @@
     <t>30</t>
   </si>
   <si>
-    <t>DXU9-8</t>
-  </si>
-  <si>
-    <t>29959</t>
-  </si>
-  <si>
-    <t>QC49F93L</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>DM2</t>
-  </si>
-  <si>
-    <t>570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (5) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BREBIERES BC - 1 (2) </t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>2VD66VPN</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
     <t>DFU11-8</t>
   </si>
   <si>
     <t>29251</t>
   </si>
   <si>
-    <t xml:space="preserve">AULNOY VALENCIENNES S (4) </t>
+    <t xml:space="preserve">AULNOY VALENCIENNES S (5) </t>
   </si>
   <si>
     <t>14:00</t>
@@ -485,19 +485,19 @@
         <v>27</v>
       </c>
       <c r="G3" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="H3" t="s" s="0">
+      <c r="I3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="I3" t="s" s="0">
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>31</v>
       </c>
       <c r="L3" t="s" s="0">
         <v>21</v>
@@ -505,22 +505,22 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="C4" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="D4" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="E4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="0">
         <v>35</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>17</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>36</v>
@@ -535,7 +535,7 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s" s="0">
         <v>21</v>
@@ -543,37 +543,37 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="C5" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="D5" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="E5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="E5" t="s" s="0">
+      <c r="G5" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="F5" t="s" s="0">
+      <c r="H5" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="G5" t="s" s="0">
+      <c r="I5" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="H5" t="s" s="0">
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
         <v>47</v>
-      </c>
-      <c r="I5" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s" s="0">
-        <v>49</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>21</v>
@@ -581,37 +581,37 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="D6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="G6" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s" s="0">
+      <c r="H6" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="G6" t="s" s="0">
+      <c r="I6" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="H6" t="s" s="0">
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
         <v>55</v>
-      </c>
-      <c r="I6" t="s" s="0">
-        <v>56</v>
-      </c>
-      <c r="J6" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>57</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>21</v>
@@ -619,37 +619,37 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="D7" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="H7" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="I7" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="E7" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="I7" t="s" s="0">
-        <v>65</v>
-      </c>
       <c r="J7" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="L7" t="s" s="0">
         <v>21</v>
@@ -657,37 +657,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F8" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s" s="0">
+      <c r="G8" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="D8" t="s" s="0">
+      <c r="H8" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="E8" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="H8" t="s" s="0">
+      <c r="I8" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="I8" t="s" s="0">
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s" s="0">
         <v>70</v>
-      </c>
-      <c r="J8" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s" s="0">
-        <v>71</v>
       </c>
       <c r="L8" t="s" s="0">
         <v>21</v>
@@ -695,37 +695,37 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s" s="0">
         <v>72</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="C9" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s" s="0">
         <v>73</v>
       </c>
-      <c r="C9" t="s" s="0">
-        <v>61</v>
-      </c>
-      <c r="D9" t="s" s="0">
+      <c r="E9" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="E9" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="F9" t="s" s="0">
+      <c r="I9" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="G9" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="H9" t="s" s="0">
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s" s="0">
         <v>76</v>
-      </c>
-      <c r="I9" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="J9" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s" s="0">
-        <v>78</v>
       </c>
       <c r="L9" t="s" s="0">
         <v>21</v>
@@ -733,37 +733,37 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="D10" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="C10" t="s" s="0">
+      <c r="E10" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D10" t="s" s="0">
+      <c r="G10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="E10" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s" s="0">
+      <c r="I10" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="G10" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="H10" t="s" s="0">
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="0">
         <v>84</v>
-      </c>
-      <c r="I10" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="J10" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s" s="0">
-        <v>85</v>
       </c>
       <c r="L10" t="s" s="0">
         <v>21</v>
@@ -771,25 +771,25 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s" s="0">
         <v>86</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="D11" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C11" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>42</v>
-      </c>
       <c r="E11" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>88</v>
@@ -827,13 +827,13 @@
         <v>95</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>96</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="J12" t="s" s="0">
         <v>21</v>
@@ -853,7 +853,7 @@
         <v>99</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>100</v>
@@ -865,7 +865,7 @@
         <v>101</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>102</v>

--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="113">
   <si>
     <t>Division</t>
   </si>
@@ -50,280 +50,304 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>DFU11-8</t>
+  </si>
+  <si>
+    <t>29269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 1 (2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
+  </si>
+  <si>
+    <t>26/09/2026</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>S. ALLENDE</t>
+  </si>
+  <si>
+    <t>4H3Q3P2W</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>DFU15-8</t>
+  </si>
+  <si>
+    <t>25672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET (1) </t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>Jules LADOUMEGUE</t>
+  </si>
+  <si>
+    <t>Y6RAYFHR</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
     <t>DXU9-8</t>
   </si>
   <si>
-    <t>29959</t>
+    <t>29985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLINES LEZ RACHES BC - 1 (2) </t>
   </si>
   <si>
     <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
   </si>
   <si>
-    <t xml:space="preserve">ST AMAND P H (1) </t>
-  </si>
-  <si>
-    <t>19/09/2026</t>
+    <t>27/09/2026</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>Marcel CERDAN</t>
+  </si>
+  <si>
+    <t>MJ8FUQFH</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>DMU15-2</t>
+  </si>
+  <si>
+    <t>8972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AULNOYE AS (1) </t>
+  </si>
+  <si>
+    <t>JEAN DEGROS</t>
+  </si>
+  <si>
+    <t>BFRWHNPK</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>DFU13-2</t>
+  </si>
+  <si>
+    <t>11262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPLEUVE L P - 3 (2) </t>
+  </si>
+  <si>
+    <t>SALLE DES SPORTS (SALLE A)</t>
+  </si>
+  <si>
+    <t>UY364R7H</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>DM2</t>
+  </si>
+  <si>
+    <t>601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC LESQUIN - 2 (6) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (5) </t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>FABRICE COURCIER</t>
+  </si>
+  <si>
+    <t>4HXW88XB</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>DFU18-2</t>
+  </si>
+  <si>
+    <t>6938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORIGNIES DOUAI AAE (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>Théo BOUTON</t>
+  </si>
+  <si>
+    <t>MPNJRY9K</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>DMU18-2</t>
+  </si>
+  <si>
+    <t>4642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIMBEAUCOURT CSL (6) </t>
+  </si>
+  <si>
+    <t>Raymond DAPVRIL</t>
+  </si>
+  <si>
+    <t>AXWTYMB6</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>PRM</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIMBEAUCOURT CSL - 1 (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (6) </t>
+  </si>
+  <si>
+    <t>F2LXCGR7</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>DMU13-8</t>
+  </si>
+  <si>
+    <t>27089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMBRES BASKET CLUB - 1 (2) </t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>TVV92LNC</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>DMU11-8</t>
+  </si>
+  <si>
+    <t>28431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT - 1 (4) </t>
+  </si>
+  <si>
+    <t>Z4AYAKDM</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>AMILOISIRS</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (5) </t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>2NH6ARMH</t>
+  </si>
+  <si>
+    <t>DFU9-8</t>
+  </si>
+  <si>
+    <t>30811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET (5) </t>
   </si>
   <si>
     <t>11:00</t>
   </si>
   <si>
-    <t>JEAN DEGROS</t>
-  </si>
-  <si>
-    <t>QC49F93L</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Non</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>DM2</t>
-  </si>
-  <si>
-    <t>570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (5) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BREBIERES BC - 1 (1) </t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>2VD66VPN</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>DMU15-2</t>
-  </si>
-  <si>
-    <t>8961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONNAING JA (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>Daniel COLMONT</t>
-  </si>
-  <si>
-    <t>P3TWKBF6</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>DMU13-8</t>
-  </si>
-  <si>
-    <t>27059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNION DECHY SIN BASKET (4) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>C.S. J MERCIER</t>
-  </si>
-  <si>
-    <t>DH7ZJNQK</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>DFU9-8</t>
-  </si>
-  <si>
-    <t>30804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONNAING JA - 1 (4) </t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>BEATRICE HEISS</t>
-  </si>
-  <si>
-    <t>PH4BW29F</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>DMU11-8</t>
-  </si>
-  <si>
-    <t>28402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORCHESIEN B C - 2 (1) </t>
-  </si>
-  <si>
-    <t>LEO LAGRANGE</t>
-  </si>
-  <si>
-    <t>WXEC6PRG</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>DMU18-2</t>
-  </si>
-  <si>
-    <t>4617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST AMAND P H (2) </t>
-  </si>
-  <si>
-    <t>20/09/2026</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>MAURICE HUGOT</t>
-  </si>
-  <si>
-    <t>M9XEW737</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>DFU13-2</t>
-  </si>
-  <si>
-    <t>11255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 2 (6) </t>
-  </si>
-  <si>
-    <t>QTZXCP4K</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>DFU18-2</t>
-  </si>
-  <si>
-    <t>6915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (1) </t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>D3YY9JVN</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>PRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (5) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET CLUB PEVELE (3) </t>
-  </si>
-  <si>
-    <t>QN8J7AVW</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>DFU15-8</t>
-  </si>
-  <si>
-    <t>25654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (2) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASKET CLUB PEVELE (5) </t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>LQ2HN8DD</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>DFU11-8</t>
-  </si>
-  <si>
-    <t>29251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AULNOY VALENCIENNES S (5) </t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>47WQM4RU</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>JQTVACAG</t>
+  </si>
+  <si>
+    <t>44</t>
   </si>
   <si>
     <t>7</t>
@@ -372,16 +396,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="9.91796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.29296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="33.890625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="45.765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="45.765625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="43.93359375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.27734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.65234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="14.37109375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="24.26171875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="10.9296875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="6.83203125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="7.4765625" customWidth="true" bestFit="true"/>
@@ -476,16 +500,16 @@
         <v>25</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s" s="0">
         <v>27</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>18</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>28</v>
@@ -517,25 +541,25 @@
         <v>34</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s" s="0">
         <v>21</v>
@@ -543,37 +567,37 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>21</v>
@@ -581,22 +605,22 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>52</v>
@@ -628,28 +652,28 @@
         <v>58</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s" s="0">
         <v>21</v>
@@ -657,37 +681,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J8" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="L8" t="s" s="0">
         <v>21</v>
@@ -695,37 +719,37 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J9" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L9" t="s" s="0">
         <v>21</v>
@@ -733,37 +757,37 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J10" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L10" t="s" s="0">
         <v>21</v>
@@ -771,37 +795,37 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L11" t="s" s="0">
         <v>21</v>
@@ -809,37 +833,37 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>96</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="J12" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" t="s" s="0">
         <v>21</v>
@@ -847,39 +871,75 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="G13" s="0"/>
+      <c r="H13" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="I13" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="E14" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="F13" t="s" s="0">
-        <v>101</v>
-      </c>
-      <c r="G13" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="H13" t="s" s="0">
-        <v>102</v>
-      </c>
-      <c r="I13" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="J13" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K13" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="L13" t="s" s="0">
+      <c r="F14" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="I14" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="L14" t="s" s="0">
         <v>21</v>
       </c>
     </row>

--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -50,6 +50,108 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>AMILOISIRS</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (5) </t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>2NH6ARMH</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>DMU11-8</t>
+  </si>
+  <si>
+    <t>28431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT - 1 (4) </t>
+  </si>
+  <si>
+    <t>26/09/2026</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>JEAN DEGROS</t>
+  </si>
+  <si>
+    <t>Z4AYAKDM</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>DFU9-8</t>
+  </si>
+  <si>
+    <t>30811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET (5) </t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>JQTVACAG</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>DMU13-8</t>
+  </si>
+  <si>
+    <t>27089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMBRES BASKET CLUB - 1 (2) </t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>TVV92LNC</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>DFU11-8</t>
   </si>
   <si>
@@ -59,12 +161,6 @@
     <t xml:space="preserve">BASKET FEMININ ESCAUDAIN PORTE DU HAINAUT - 1 (2) </t>
   </si>
   <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
-  </si>
-  <si>
-    <t>26/09/2026</t>
-  </si>
-  <si>
     <t>13:45</t>
   </si>
   <si>
@@ -77,12 +173,33 @@
     <t>30</t>
   </si>
   <si>
-    <t>Non</t>
-  </si>
-  <si>
     <t>15</t>
   </si>
   <si>
+    <t>DMU15-2</t>
+  </si>
+  <si>
+    <t>8972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AULNOYE AS (1) </t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>BFRWHNPK</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
     <t>DFU15-8</t>
   </si>
   <si>
@@ -92,9 +209,6 @@
     <t xml:space="preserve">UNION DECHY SIN BASKET (1) </t>
   </si>
   <si>
-    <t>17:00</t>
-  </si>
-  <si>
     <t>Jules LADOUMEGUE</t>
   </si>
   <si>
@@ -116,15 +230,9 @@
     <t xml:space="preserve">FLINES LEZ RACHES BC - 1 (2) </t>
   </si>
   <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
-  </si>
-  <si>
     <t>27/09/2026</t>
   </si>
   <si>
-    <t>14:00</t>
-  </si>
-  <si>
     <t>Marcel CERDAN</t>
   </si>
   <si>
@@ -137,30 +245,6 @@
     <t>21</t>
   </si>
   <si>
-    <t>DMU15-2</t>
-  </si>
-  <si>
-    <t>8972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AULNOYE AS (1) </t>
-  </si>
-  <si>
-    <t>JEAN DEGROS</t>
-  </si>
-  <si>
-    <t>BFRWHNPK</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
     <t>DFU13-2</t>
   </si>
   <si>
@@ -182,6 +266,27 @@
     <t>18</t>
   </si>
   <si>
+    <t>DMU18-2</t>
+  </si>
+  <si>
+    <t>4642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIMBEAUCOURT CSL (6) </t>
+  </si>
+  <si>
+    <t>Raymond DAPVRIL</t>
+  </si>
+  <si>
+    <t>AXWTYMB6</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
     <t>DM2</t>
   </si>
   <si>
@@ -203,9 +308,6 @@
     <t>4HXW88XB</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>DFU18-2</t>
   </si>
   <si>
@@ -230,27 +332,6 @@
     <t>48</t>
   </si>
   <si>
-    <t>DMU18-2</t>
-  </si>
-  <si>
-    <t>4642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAIMBEAUCOURT CSL (6) </t>
-  </si>
-  <si>
-    <t>Raymond DAPVRIL</t>
-  </si>
-  <si>
-    <t>AXWTYMB6</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
     <t>PRM</t>
   </si>
   <si>
@@ -270,87 +351,6 @@
   </si>
   <si>
     <t>66</t>
-  </si>
-  <si>
-    <t>DMU13-8</t>
-  </si>
-  <si>
-    <t>27089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMBRES BASKET CLUB - 1 (2) </t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>TVV92LNC</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>DMU11-8</t>
-  </si>
-  <si>
-    <t>28431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT - 1 (4) </t>
-  </si>
-  <si>
-    <t>Z4AYAKDM</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>AMILOISIRS</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (5) </t>
-  </si>
-  <si>
-    <t>23/09/2026</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>2NH6ARMH</t>
-  </si>
-  <si>
-    <t>DFU9-8</t>
-  </si>
-  <si>
-    <t>30811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNION DECHY SIN BASKET (5) </t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>JQTVACAG</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -470,40 +470,38 @@
       <c r="F2" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" s="0"/>
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="I2" t="s" s="0">
-        <v>20</v>
-      </c>
       <c r="J2" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="D3" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>16</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>26</v>
@@ -518,13 +516,13 @@
         <v>29</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K3" t="s" s="0">
         <v>30</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -541,368 +539,370 @@
         <v>34</v>
       </c>
       <c r="E4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="F4" t="s" s="0">
+      <c r="G4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="G4" t="s" s="0">
+      <c r="I4" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="H4" t="s" s="0">
+      <c r="J4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="I4" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s" s="0">
-        <v>40</v>
-      </c>
       <c r="L4" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="E5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="G5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="I5" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="E5" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s" s="0">
+      <c r="J5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="H5" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="I5" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s" s="0">
-        <v>48</v>
-      </c>
       <c r="L5" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="G6" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="H6" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s" s="0">
+      <c r="I6" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="H6" t="s" s="0">
+      <c r="J6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="I6" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="J6" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>55</v>
-      </c>
       <c r="L6" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="D7" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="E7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="G7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="H7" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="E7" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="F7" t="s" s="0">
+      <c r="I7" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="G7" t="s" s="0">
+      <c r="J7" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="H7" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="I7" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="J7" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K7" t="s" s="0">
-        <v>63</v>
-      </c>
       <c r="L7" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="D8" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="C8" t="s" s="0">
+      <c r="H8" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="D8" t="s" s="0">
+      <c r="I8" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="E8" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s" s="0">
+      <c r="J8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="G8" t="s" s="0">
-        <v>69</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="I8" t="s" s="0">
-        <v>71</v>
-      </c>
-      <c r="J8" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s" s="0">
-        <v>47</v>
-      </c>
       <c r="L8" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s" s="0">
         <v>72</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>16</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>26</v>
       </c>
       <c r="G9" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="H9" t="s" s="0">
+      <c r="J9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="I9" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="J9" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s" s="0">
-        <v>78</v>
-      </c>
       <c r="L9" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="D10" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="C10" t="s" s="0">
+      <c r="H10" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D10" t="s" s="0">
+      <c r="I10" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="E10" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>75</v>
-      </c>
-      <c r="H10" t="s" s="0">
+      <c r="J10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="I10" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="J10" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s" s="0">
-        <v>85</v>
-      </c>
       <c r="L10" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s" s="0">
         <v>86</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="D11" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="C11" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s" s="0">
+      <c r="H11" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="E11" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s" s="0">
+      <c r="I11" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="G11" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="H11" t="s" s="0">
+      <c r="J11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K11" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="I11" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="J11" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K11" t="s" s="0">
-        <v>92</v>
-      </c>
       <c r="L11" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="D12" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="C12" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s" s="0">
+      <c r="E12" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="E12" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>36</v>
-      </c>
       <c r="G12" t="s" s="0">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="L12" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B13" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="C13" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="C13" t="s" s="0">
+      <c r="D13" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="D13" t="s" s="0">
+      <c r="E13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="E13" t="s" s="0">
+      <c r="G13" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="F13" t="s" s="0">
+      <c r="H13" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="G13" s="0"/>
-      <c r="H13" t="s" s="0">
+      <c r="I13" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="I13" t="s" s="0">
-        <v>63</v>
-      </c>
       <c r="J13" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L13" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -913,19 +913,19 @@
         <v>107</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>110</v>
@@ -934,13 +934,13 @@
         <v>111</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s" s="0">
         <v>112</v>
       </c>
       <c r="L14" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="111">
   <si>
     <t>Division</t>
   </si>
@@ -50,274 +50,301 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>DFU18-2</t>
+  </si>
+  <si>
+    <t>6985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUAI BASKET FEMININ - 3 (2) </t>
+  </si>
+  <si>
+    <t>10/10/2026</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>JEAN DEGROS</t>
+  </si>
+  <si>
+    <t>PD9E7UAJ</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
     <t>DMU13-8</t>
   </si>
   <si>
-    <t>27118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BREBIERES BC (3) </t>
+    <t>27149</t>
   </si>
   <si>
     <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (4) </t>
   </si>
   <si>
-    <t>03/10/2026</t>
+    <t xml:space="preserve">CUINCY ASB (5) </t>
   </si>
   <si>
     <t>15:30</t>
   </si>
   <si>
-    <t>FRANCOIS ANACHE</t>
-  </si>
-  <si>
-    <t>VLLGEDRM</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>Non</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>HKQQ9ZK6</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>PRM</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEUNESSE BASKET CLUB AUBY - 1 (2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (3) </t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>Michel DUJARDIN</t>
+  </si>
+  <si>
+    <t>67R9L4D3</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>DM2</t>
+  </si>
+  <si>
+    <t>660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION DECHY SIN BASKET - 3 (6) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (2) </t>
+  </si>
+  <si>
+    <t>Jules LADOUMEGUE</t>
+  </si>
+  <si>
+    <t>ZAVGYKLJ</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>DFU13-2</t>
+  </si>
+  <si>
+    <t>11273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCQ EN BAROEUL ASJ (1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
+  </si>
+  <si>
+    <t>SALLE LAZARO</t>
+  </si>
+  <si>
+    <t>96244FCY</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>DFU15-8</t>
+  </si>
+  <si>
+    <t>25708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUINCY ASB (3) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (2) </t>
+  </si>
+  <si>
+    <t>Jean LENNE</t>
+  </si>
+  <si>
+    <t>GFQAAW8G</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>DFU11-8</t>
+  </si>
+  <si>
+    <t>29305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAC SOMAIN MARCHIENNES BASKETBALL (3) </t>
+  </si>
+  <si>
+    <t>11/10/2026</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>Léo LAGRANGE</t>
+  </si>
+  <si>
+    <t>LBPWHCJR</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>DMU11-8</t>
+  </si>
+  <si>
+    <t>28493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAYANT BASKET (4) </t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste COROT</t>
+  </si>
+  <si>
+    <t>27BFVHNG</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>DMU15-2</t>
+  </si>
+  <si>
+    <t>8998</t>
+  </si>
+  <si>
+    <t>Exempt</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>AMILOISIRS</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAUDRY BC (14) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (1) </t>
+  </si>
+  <si>
+    <t>YC7348KG</t>
+  </si>
+  <si>
+    <t>68</t>
   </si>
   <si>
     <t>DXU9-8</t>
   </si>
   <si>
-    <t>30011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAYANT BASKET (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
-  </si>
-  <si>
-    <t>04/10/2026</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>Jean-Baptiste COROT</t>
-  </si>
-  <si>
-    <t>CA4VJ4RY</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>DFU18-2</t>
-  </si>
-  <si>
-    <t>6961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNION DECHY SIN BASKET (4) </t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>C.S. J MERCIER</t>
-  </si>
-  <si>
-    <t>ATLFJF24</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>52</t>
+    <t>30038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREBIERES BC (5) </t>
+  </si>
+  <si>
+    <t>9A7D4GKK</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>DFU9-8</t>
   </si>
   <si>
-    <t>30818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEUVRAGES ASM (5) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (2) </t>
-  </si>
-  <si>
-    <t>Léo LAGRANGE</t>
-  </si>
-  <si>
-    <t>MQR3F3TV</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>30825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AULNOY VALENCIENNES S (7) </t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>4LLW2NFM</t>
   </si>
   <si>
     <t>44</t>
   </si>
   <si>
-    <t>DM2</t>
-  </si>
-  <si>
-    <t>629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (4) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECLIN BC - 2 (3) </t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>JEAN DEGROS</t>
-  </si>
-  <si>
-    <t>LTQ44U4A</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>DMU11-8</t>
-  </si>
-  <si>
-    <t>28463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASC DENAIN VOLTAIRE PORTE DU HAINAUT - 2 (2) </t>
-  </si>
-  <si>
-    <t>CLU6QF92</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>DMU15-2</t>
-  </si>
-  <si>
-    <t>8986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASC DENAIN VOLTAIRE PORTE DU HAINAUT - 2 (1) </t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>UXPJCJCJ</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>0</t>
   </si>
   <si>
     <t>DMU18-2</t>
   </si>
   <si>
-    <t>4664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HASNON BASKET - 2 (1) </t>
-  </si>
-  <si>
-    <t>MMH9JNJ6</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>PRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (4) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST AMAND P H - 1 (6) </t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>83Z2QJEY</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>DFU13-2</t>
-  </si>
-  <si>
-    <t>11266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST AMAND P H (3) </t>
-  </si>
-  <si>
-    <t>TCLX632J</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>DFU11-8</t>
-  </si>
-  <si>
-    <t>29288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT (4) </t>
-  </si>
-  <si>
-    <t>ZK99WAYV</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>DFU15-8</t>
-  </si>
-  <si>
-    <t>25691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (3) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT (6) </t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>AL87R7BZ</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>31</t>
+    <t>4689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMBRES BASKET CLUB - 2 (3) </t>
+  </si>
+  <si>
+    <t>QN2KE6N8</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>97</t>
   </si>
 </sst>
 </file>
@@ -363,13 +390,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="9.91796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.29296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="33.890625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="41.3671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="37.88671875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="33.890625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.27734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.65234375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="17.46875" customWidth="true" bestFit="true"/>
@@ -470,25 +497,25 @@
         <v>26</v>
       </c>
       <c r="E3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="F3" t="s" s="0">
+      <c r="G3" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="G3" t="s" s="0">
+      <c r="I3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="H3" t="s" s="0">
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>32</v>
       </c>
       <c r="L3" t="s" s="0">
         <v>21</v>
@@ -496,37 +523,37 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="D4" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="E4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="D4" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s" s="0">
+      <c r="G4" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="G4" t="s" s="0">
+      <c r="H4" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="H4" t="s" s="0">
+      <c r="I4" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="I4" t="s" s="0">
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
         <v>39</v>
-      </c>
-      <c r="J4" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s" s="0">
-        <v>40</v>
       </c>
       <c r="L4" t="s" s="0">
         <v>21</v>
@@ -534,37 +561,37 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="C5" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="D5" t="s" s="0">
         <v>43</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>44</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="H5" t="s" s="0">
+      <c r="I5" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="I5" t="s" s="0">
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
         <v>47</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s" s="0">
-        <v>48</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>21</v>
@@ -572,37 +599,37 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="C6" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="D6" t="s" s="0">
         <v>51</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>52</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="G6" t="s" s="0">
+      <c r="I6" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="H6" t="s" s="0">
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
         <v>55</v>
-      </c>
-      <c r="I6" t="s" s="0">
-        <v>56</v>
-      </c>
-      <c r="J6" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>57</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>21</v>
@@ -610,25 +637,25 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="D7" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="C7" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s" s="0">
+      <c r="E7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s" s="0">
         <v>60</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>54</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>61</v>
@@ -654,31 +681,31 @@
         <v>65</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J8" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L8" t="s" s="0">
         <v>21</v>
@@ -686,37 +713,37 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="J9" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L9" t="s" s="0">
         <v>21</v>
@@ -724,37 +751,35 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>79</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>54</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G10" s="0"/>
       <c r="H10" t="s" s="0">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L10" t="s" s="0">
         <v>21</v>
@@ -762,37 +787,35 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="G11" t="s" s="0">
-        <v>54</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G11" s="0"/>
       <c r="H11" t="s" s="0">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="J11" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="L11" t="s" s="0">
         <v>21</v>
@@ -800,37 +823,37 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J12" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L12" t="s" s="0">
         <v>21</v>
@@ -838,39 +861,77 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J13" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L13" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="I14" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="L14" t="s" s="0">
         <v>21</v>
       </c>
     </row>

--- a/data/resultats/resultats.xlsx
+++ b/data/resultats/resultats.xlsx
@@ -50,6 +50,39 @@
     <t>Forfait 2</t>
   </si>
   <si>
+    <t>DMU11-8</t>
+  </si>
+  <si>
+    <t>28523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREBIERES BC (6) </t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>JEAN DEGROS</t>
+  </si>
+  <si>
+    <t>9UDZ2ZGP</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>DFU15-8</t>
   </si>
   <si>
@@ -62,24 +95,12 @@
     <t xml:space="preserve">BREBIERES BC (4) </t>
   </si>
   <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
     <t>17:00</t>
   </si>
   <si>
-    <t>JEAN DEGROS</t>
-  </si>
-  <si>
     <t>A4A44MUC</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>Non</t>
-  </si>
-  <si>
     <t>35</t>
   </si>
   <si>
@@ -89,9 +110,6 @@
     <t>29323</t>
   </si>
   <si>
-    <t xml:space="preserve">BREBIERES BC (6) </t>
-  </si>
-  <si>
     <t>14:00</t>
   </si>
   <si>
@@ -104,22 +122,28 @@
     <t>10</t>
   </si>
   <si>
-    <t>DMU11-8</t>
-  </si>
-  <si>
-    <t>28523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (5) </t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>9UDZ2ZGP</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>DFU18-2</t>
+  </si>
+  <si>
+    <t>7011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT - 2 (1) </t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>64Y8HJ6Y</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>80</t>
   </si>
   <si>
     <t>DMU15-2</t>
@@ -143,6 +167,30 @@
     <t>73</t>
   </si>
   <si>
+    <t>DM2</t>
+  </si>
+  <si>
+    <t>689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUINCY ASB (4) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (2) </t>
+  </si>
+  <si>
+    <t>Jean LENNE</t>
+  </si>
+  <si>
+    <t>TYQDQK3L</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
     <t>DFU9-8</t>
   </si>
   <si>
@@ -158,39 +206,12 @@
     <t>12</t>
   </si>
   <si>
-    <t>DM2</t>
-  </si>
-  <si>
-    <t>689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUINCY ASB (4) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 2 (2) </t>
-  </si>
-  <si>
-    <t>Jean LENNE</t>
-  </si>
-  <si>
-    <t>TYQDQK3L</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
     <t>PRM</t>
   </si>
   <si>
     <t>112</t>
   </si>
   <si>
-    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT - 2 (3) </t>
-  </si>
-  <si>
     <t xml:space="preserve">AMICALE BASKET PECQUENCOURT - 1 (5) </t>
   </si>
   <si>
@@ -206,7 +227,10 @@
     <t>VLPR4CMA</t>
   </si>
   <si>
-    <t/>
+    <t>54</t>
+  </si>
+  <si>
+    <t>52</t>
   </si>
   <si>
     <t>DMU18-2</t>
@@ -245,9 +269,6 @@
     <t>JBJGRZMN</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -294,27 +315,6 @@
   </si>
   <si>
     <t>25</t>
-  </si>
-  <si>
-    <t>DFU18-2</t>
-  </si>
-  <si>
-    <t>7011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMICALE BASKET PECQUENCOURT (6) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTREVENT BASKET BALL EAA MONCHECOURT - 2 (1) </t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>64Y8HJ6Y</t>
-  </si>
-  <si>
-    <t>80</t>
   </si>
 </sst>
 </file>
@@ -461,25 +461,25 @@
         <v>24</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>18</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>21</v>
@@ -499,25 +499,25 @@
         <v>31</v>
       </c>
       <c r="C4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="0">
         <v>32</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>33</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>18</v>
       </c>
       <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="I4" t="s" s="0">
-        <v>20</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>21</v>
@@ -537,31 +537,31 @@
         <v>37</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>18</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>21</v>
@@ -569,37 +569,37 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J6" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>21</v>
@@ -607,37 +607,37 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L7" t="s" s="0">
         <v>21</v>
@@ -645,37 +645,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="G8" t="s" s="0">
+      <c r="H8" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="H8" t="s" s="0">
+      <c r="I8" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="I8" t="s" s="0">
-        <v>64</v>
-      </c>
       <c r="J8" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="L8" t="s" s="0">
         <v>21</v>
@@ -683,37 +683,37 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B9" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="C9" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="C9" t="s" s="0">
+      <c r="E9" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="D9" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>16</v>
-      </c>
       <c r="F9" t="s" s="0">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L9" t="s" s="0">
         <v>21</v>
@@ -721,37 +721,37 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s" s="0">
         <v>21</v>
@@ -759,22 +759,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>16</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>83</v>
@@ -783,13 +783,13 @@
         <v>84</v>
       </c>
       <c r="I11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s" s="0">
         <v>85</v>
-      </c>
-      <c r="J11" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K11" t="s" s="0">
-        <v>28</v>
       </c>
       <c r="L11" t="s" s="0">
         <v>21</v>
@@ -806,13 +806,13 @@
         <v>88</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>90</v>
@@ -827,7 +827,7 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="L12" t="s" s="0">
         <v>21</v>
@@ -835,31 +835,31 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="C13" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="C13" t="s" s="0">
+      <c r="D13" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F13" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="D13" t="s" s="0">
+      <c r="G13" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="E13" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F13" t="s" s="0">
+      <c r="H13" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="G13" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="H13" t="s" s="0">
+      <c r="I13" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="I13" t="s" s="0">
-        <v>77</v>
       </c>
       <c r="J13" t="s" s="0">
         <v>21</v>
